--- a/excel_bai_tap/bai3_bang_phan_bo_tien_thuong.xlsx
+++ b/excel_bai_tap/bai3_bang_phan_bo_tien_thuong.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t xml:space="preserve">BẢNG PHÂN BỐ TIỀN THƯỞNG NĂM 2000</t>
   </si>
@@ -68,24 +68,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cao nhất | Thấp nhất | Bình quân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yêu cầu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính số tháng làm việc =Tổng số tháng- tháng bắt đầu. Biết tổng số tháng: 13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiền thưởng =(Tổng tiền thưởng *Số tháng)/Tổng số tháng, làm tròn một số thập phân biết rằng Tổng tiền thưởng của công ty: 20.000.000 đồng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bảo hiểm = tiền thưởng *7.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số tiền lãnh = số tiền thưởng - BHXH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính tiền thưởng cao nhất , BHXH thấp nhất , Bình quân số tiền lãnh.</t>
   </si>
   <si>
     <t xml:space="preserve">Tham số (ô nhập, tô vàng):</t>
@@ -111,7 +93,7 @@
     <numFmt numFmtId="167" formatCode="#,##0"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,14 +142,6 @@
     <font>
       <b val="true"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="0"/>
@@ -254,7 +228,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -295,23 +269,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -567,7 +537,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -630,15 +600,15 @@
         <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
-        <f aca="false">$C$20-D3</f>
+        <f aca="false">$C$12-D3</f>
         <v>12</v>
       </c>
       <c r="F3" s="5" t="n">
-        <f aca="false">ROUND(($C$21*E3)/$C$20,1)</f>
+        <f aca="false">ROUND(($C$13*E3)/$C$12,1)</f>
         <v>18461538.5</v>
       </c>
       <c r="G3" s="6" t="n">
-        <f aca="false">F3*$C$22</f>
+        <f aca="false">F3*$C$14</f>
         <v>1384615.3875</v>
       </c>
       <c r="H3" s="7" t="n">
@@ -660,15 +630,15 @@
         <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
-        <f aca="false">$C$20-D4</f>
+        <f aca="false">$C$12-D4</f>
         <v>12</v>
       </c>
       <c r="F4" s="5" t="n">
-        <f aca="false">ROUND(($C$21*E4)/$C$20,1)</f>
+        <f aca="false">ROUND(($C$13*E4)/$C$12,1)</f>
         <v>18461538.5</v>
       </c>
       <c r="G4" s="6" t="n">
-        <f aca="false">F4*$C$22</f>
+        <f aca="false">F4*$C$14</f>
         <v>1384615.3875</v>
       </c>
       <c r="H4" s="7" t="n">
@@ -690,15 +660,15 @@
         <v>2</v>
       </c>
       <c r="E5" s="3" t="n">
-        <f aca="false">$C$20-D5</f>
+        <f aca="false">$C$12-D5</f>
         <v>11</v>
       </c>
       <c r="F5" s="5" t="n">
-        <f aca="false">ROUND(($C$21*E5)/$C$20,1)</f>
+        <f aca="false">ROUND(($C$13*E5)/$C$12,1)</f>
         <v>16923076.9</v>
       </c>
       <c r="G5" s="6" t="n">
-        <f aca="false">F5*$C$22</f>
+        <f aca="false">F5*$C$14</f>
         <v>1269230.7675</v>
       </c>
       <c r="H5" s="7" t="n">
@@ -720,15 +690,15 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="n">
-        <f aca="false">$C$20-D6</f>
+        <f aca="false">$C$12-D6</f>
         <v>8</v>
       </c>
       <c r="F6" s="5" t="n">
-        <f aca="false">ROUND(($C$21*E6)/$C$20,1)</f>
+        <f aca="false">ROUND(($C$13*E6)/$C$12,1)</f>
         <v>12307692.3</v>
       </c>
       <c r="G6" s="6" t="n">
-        <f aca="false">F6*$C$22</f>
+        <f aca="false">F6*$C$14</f>
         <v>923076.9225</v>
       </c>
       <c r="H6" s="7" t="n">
@@ -750,15 +720,15 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
-        <f aca="false">$C$20-D7</f>
+        <f aca="false">$C$12-D7</f>
         <v>12</v>
       </c>
       <c r="F7" s="5" t="n">
-        <f aca="false">ROUND(($C$21*E7)/$C$20,1)</f>
+        <f aca="false">ROUND(($C$13*E7)/$C$12,1)</f>
         <v>18461538.5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <f aca="false">F7*$C$22</f>
+        <f aca="false">F7*$C$14</f>
         <v>1384615.3875</v>
       </c>
       <c r="H7" s="7" t="n">
@@ -780,15 +750,15 @@
         <v>7</v>
       </c>
       <c r="E8" s="3" t="n">
-        <f aca="false">$C$20-D8</f>
+        <f aca="false">$C$12-D8</f>
         <v>6</v>
       </c>
       <c r="F8" s="5" t="n">
-        <f aca="false">ROUND(($C$21*E8)/$C$20,1)</f>
+        <f aca="false">ROUND(($C$13*E8)/$C$12,1)</f>
         <v>9230769.2</v>
       </c>
       <c r="G8" s="6" t="n">
-        <f aca="false">F8*$C$22</f>
+        <f aca="false">F8*$C$14</f>
         <v>692307.69</v>
       </c>
       <c r="H8" s="7" t="n">
@@ -813,62 +783,32 @@
         <v>14467948.72625</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
+      <c r="C12" s="11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="C13" s="12" t="n">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="14" t="n">
+      <c r="C14" s="13" t="n">
         <v>0.075</v>
       </c>
     </row>

--- a/excel_bai_tap/bai3_bang_phan_bo_tien_thuong.xlsx
+++ b/excel_bai_tap/bai3_bang_phan_bo_tien_thuong.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">BẢNG PHÂN BỐ TIỀN THƯỞNG NĂM 2000</t>
   </si>
@@ -65,35 +65,17 @@
   </si>
   <si>
     <t xml:space="preserve">Nguyễn Mỹ Dung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cao nhất | Thấp nhất | Bình quân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tham số (ô nhập, tô vàng):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tổng số tháng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tổng tiền thưởng của công ty (đồng)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tỉ lệ bảo hiểm XH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,15 +129,8 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0000FF"/>
-      <name val="Times New Roman"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -180,12 +155,6 @@
         <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -228,7 +197,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -261,27 +230,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -537,7 +486,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -600,15 +549,15 @@
         <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
-        <f aca="false">$C$12-D3</f>
+        <f aca="false">13-D3</f>
         <v>12</v>
       </c>
       <c r="F3" s="5" t="n">
-        <f aca="false">ROUND(($C$13*E3)/$C$12,1)</f>
+        <f aca="false">ROUND((20000000*E3)/13,1)</f>
         <v>18461538.5</v>
       </c>
       <c r="G3" s="6" t="n">
-        <f aca="false">F3*$C$14</f>
+        <f aca="false">F3*0.075</f>
         <v>1384615.3875</v>
       </c>
       <c r="H3" s="7" t="n">
@@ -630,15 +579,15 @@
         <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
-        <f aca="false">$C$12-D4</f>
+        <f aca="false">13-D4</f>
         <v>12</v>
       </c>
       <c r="F4" s="5" t="n">
-        <f aca="false">ROUND(($C$13*E4)/$C$12,1)</f>
+        <f aca="false">ROUND((20000000*E4)/13,1)</f>
         <v>18461538.5</v>
       </c>
       <c r="G4" s="6" t="n">
-        <f aca="false">F4*$C$14</f>
+        <f aca="false">F4*0.075</f>
         <v>1384615.3875</v>
       </c>
       <c r="H4" s="7" t="n">
@@ -660,15 +609,15 @@
         <v>2</v>
       </c>
       <c r="E5" s="3" t="n">
-        <f aca="false">$C$12-D5</f>
+        <f aca="false">13-D5</f>
         <v>11</v>
       </c>
       <c r="F5" s="5" t="n">
-        <f aca="false">ROUND(($C$13*E5)/$C$12,1)</f>
+        <f aca="false">ROUND((20000000*E5)/13,1)</f>
         <v>16923076.9</v>
       </c>
       <c r="G5" s="6" t="n">
-        <f aca="false">F5*$C$14</f>
+        <f aca="false">F5*0.075</f>
         <v>1269230.7675</v>
       </c>
       <c r="H5" s="7" t="n">
@@ -690,15 +639,15 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="n">
-        <f aca="false">$C$12-D6</f>
+        <f aca="false">13-D6</f>
         <v>8</v>
       </c>
       <c r="F6" s="5" t="n">
-        <f aca="false">ROUND(($C$13*E6)/$C$12,1)</f>
+        <f aca="false">ROUND((20000000*E6)/13,1)</f>
         <v>12307692.3</v>
       </c>
       <c r="G6" s="6" t="n">
-        <f aca="false">F6*$C$14</f>
+        <f aca="false">F6*0.075</f>
         <v>923076.9225</v>
       </c>
       <c r="H6" s="7" t="n">
@@ -720,15 +669,15 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
-        <f aca="false">$C$12-D7</f>
+        <f aca="false">13-D7</f>
         <v>12</v>
       </c>
       <c r="F7" s="5" t="n">
-        <f aca="false">ROUND(($C$13*E7)/$C$12,1)</f>
+        <f aca="false">ROUND((20000000*E7)/13,1)</f>
         <v>18461538.5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <f aca="false">F7*$C$14</f>
+        <f aca="false">F7*0.075</f>
         <v>1384615.3875</v>
       </c>
       <c r="H7" s="7" t="n">
@@ -750,15 +699,15 @@
         <v>7</v>
       </c>
       <c r="E8" s="3" t="n">
-        <f aca="false">$C$12-D8</f>
+        <f aca="false">13-D8</f>
         <v>6</v>
       </c>
       <c r="F8" s="5" t="n">
-        <f aca="false">ROUND(($C$13*E8)/$C$12,1)</f>
+        <f aca="false">ROUND((20000000*E8)/13,1)</f>
         <v>9230769.2</v>
       </c>
       <c r="G8" s="6" t="n">
-        <f aca="false">F8*$C$14</f>
+        <f aca="false">F8*0.075</f>
         <v>692307.69</v>
       </c>
       <c r="H8" s="7" t="n">
@@ -767,49 +716,17 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <f aca="false">MAX(F3:F8)</f>
         <v>18461538.5</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <f aca="false">MIN(G3:G8)</f>
         <v>692307.69</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="8" t="n">
         <f aca="false">AVERAGE(H3:H8)</f>
         <v>14467948.72625</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>0.075</v>
       </c>
     </row>
   </sheetData>
